--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92511</v>
+        <v>92512</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78872</v>
+        <v>78875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92512</v>
+        <v>92515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92352</v>
+        <v>92355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92503</v>
+        <v>92506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>137308822</v>
       </c>
       <c r="B52" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>137308771</v>
       </c>
       <c r="B53" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80584</v>
+        <v>80587</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92515</v>
+        <v>92517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78875</v>
+        <v>78880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92357</v>
+        <v>92362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92508</v>
+        <v>92513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>137308822</v>
       </c>
       <c r="B52" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>137308771</v>
       </c>
       <c r="B53" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80587</v>
+        <v>80592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78880</v>
+        <v>78891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92522</v>
+        <v>92534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92362</v>
+        <v>92374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92513</v>
+        <v>92525</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80592</v>
+        <v>80603</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78891</v>
+        <v>78892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92374</v>
+        <v>92375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92525</v>
+        <v>92526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80603</v>
+        <v>80604</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78892</v>
+        <v>78894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92535</v>
+        <v>92538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92375</v>
+        <v>92378</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80604</v>
+        <v>80606</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 14892-2026 artfynd.xlsx
+++ b/artfynd/A 14892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308788</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308761</v>
       </c>
       <c r="B3" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308809</v>
       </c>
       <c r="B4" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308767</v>
       </c>
       <c r="B5" t="n">
-        <v>78894</v>
+        <v>78898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308791</v>
       </c>
       <c r="B6" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308803</v>
       </c>
       <c r="B7" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308811</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308782</v>
       </c>
       <c r="B9" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308800</v>
       </c>
       <c r="B10" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308817</v>
       </c>
       <c r="B11" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308818</v>
       </c>
       <c r="B12" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308766</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308769</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308774</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308796</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308798</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308802</v>
       </c>
       <c r="B18" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308763</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308775</v>
       </c>
       <c r="B20" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308797</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308815</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308758</v>
       </c>
       <c r="B23" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137308804</v>
       </c>
       <c r="B24" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137308813</v>
       </c>
       <c r="B25" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137308757</v>
       </c>
       <c r="B26" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137308792</v>
       </c>
       <c r="B27" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308821</v>
       </c>
       <c r="B28" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308773</v>
       </c>
       <c r="B29" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308806</v>
       </c>
       <c r="B30" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308807</v>
       </c>
       <c r="B31" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308808</v>
       </c>
       <c r="B32" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308823</v>
       </c>
       <c r="B33" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308764</v>
       </c>
       <c r="B34" t="n">
-        <v>92538</v>
+        <v>92542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>137308768</v>
       </c>
       <c r="B35" t="n">
-        <v>92378</v>
+        <v>92382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>137308812</v>
       </c>
       <c r="B36" t="n">
-        <v>92529</v>
+        <v>92533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>137308785</v>
       </c>
       <c r="B37" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>137308781</v>
       </c>
       <c r="B38" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>137308784</v>
       </c>
       <c r="B39" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>137308799</v>
       </c>
       <c r="B40" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>137308756</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>137308762</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137308770</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>137308794</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>137308778</v>
       </c>
       <c r="B45" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>137308780</v>
       </c>
       <c r="B46" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137308789</v>
       </c>
       <c r="B47" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137308810</v>
       </c>
       <c r="B48" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>137308820</v>
       </c>
       <c r="B49" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>137308779</v>
       </c>
       <c r="B50" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>137308822</v>
       </c>
       <c r="B52" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>137308771</v>
       </c>
       <c r="B53" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>137308787</v>
       </c>
       <c r="B54" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>137308814</v>
       </c>
       <c r="B55" t="n">
-        <v>80606</v>
+        <v>80610</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
